--- a/logs/logs_mar.xlsx
+++ b/logs/logs_mar.xlsx
@@ -522,16 +522,16 @@
         <v>2.599999999999909</v>
       </c>
       <c r="F3" t="n">
-        <v>2179891.999999924</v>
+        <v>14299.9999999995</v>
       </c>
       <c r="G3" t="n">
-        <v>3437521.999999924</v>
+        <v>1271930</v>
       </c>
       <c r="H3" t="n">
         <v>-449730</v>
       </c>
       <c r="I3" t="n">
-        <v>2179891.999999924</v>
+        <v>14299.99999999953</v>
       </c>
       <c r="J3" t="n">
         <v>-115.7687622303027</v>
@@ -557,19 +557,19 @@
         <v>7.600000000000023</v>
       </c>
       <c r="F4" t="n">
-        <v>6371992.000000019</v>
+        <v>41800.00000000012</v>
       </c>
       <c r="G4" t="n">
-        <v>9809513.999999942</v>
+        <v>1313730</v>
       </c>
       <c r="H4" t="n">
         <v>-449730</v>
       </c>
       <c r="I4" t="n">
-        <v>8551883.999999942</v>
+        <v>56099.99999999977</v>
       </c>
       <c r="J4" t="n">
-        <v>202.3178040951231</v>
+        <v>-113.6821277096688</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -592,19 +592,19 @@
         <v>15.25</v>
       </c>
       <c r="F5" t="n">
-        <v>12785905</v>
+        <v>83875</v>
       </c>
       <c r="G5" t="n">
-        <v>22595418.99999994</v>
+        <v>1397605</v>
       </c>
       <c r="H5" t="n">
         <v>-449730</v>
       </c>
       <c r="I5" t="n">
-        <v>21337788.99999994</v>
+        <v>139974.9999999998</v>
       </c>
       <c r="J5" t="n">
-        <v>1132.109305661788</v>
+        <v>-107.582734495508</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -627,19 +627,19 @@
         <v>-3.299999999999955</v>
       </c>
       <c r="F6" t="n">
-        <v>-2766785.999999962</v>
+        <v>-18149.99999999975</v>
       </c>
       <c r="G6" t="n">
-        <v>19828632.99999998</v>
+        <v>1379455</v>
       </c>
       <c r="H6" t="n">
         <v>-449730</v>
       </c>
       <c r="I6" t="n">
-        <v>18571002.99999998</v>
+        <v>121825</v>
       </c>
       <c r="J6" t="n">
-        <v>2997.809358147523</v>
+        <v>-95.3438204802513</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -662,19 +662,19 @@
         <v>-13.85000000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>-11612117.00000002</v>
+        <v>-76175.00000000013</v>
       </c>
       <c r="G7" t="n">
-        <v>8216515.999999959</v>
+        <v>1303280</v>
       </c>
       <c r="H7" t="n">
         <v>-449730</v>
       </c>
       <c r="I7" t="n">
-        <v>6958885.999999959</v>
+        <v>45649.99999999977</v>
       </c>
       <c r="J7" t="n">
-        <v>2594.08410088832</v>
+        <v>-97.99224121797894</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -697,22 +697,22 @@
         <v>-10.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-8593805</v>
+        <v>-56375</v>
       </c>
       <c r="G8" t="n">
-        <v>1257630</v>
+        <v>1246905</v>
       </c>
       <c r="H8" t="n">
-        <v>-2084649.000000041</v>
+        <v>-449730</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>899.6614302701247</v>
+        <v>-109.1075827990482</v>
       </c>
       <c r="K8" t="n">
-        <v>1634919.000000041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -732,19 +732,19 @@
         <v>6.950000000000045</v>
       </c>
       <c r="F9" t="n">
-        <v>5827019.000000038</v>
+        <v>38225.00000000025</v>
       </c>
       <c r="G9" t="n">
-        <v>7084649.000000038</v>
+        <v>1285130</v>
       </c>
       <c r="H9" t="n">
-        <v>-2084649.000000041</v>
+        <v>-449730</v>
       </c>
       <c r="I9" t="n">
-        <v>5827019.000000038</v>
+        <v>27500</v>
       </c>
       <c r="J9" t="n">
-        <v>-536.6269415307917</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -767,19 +767,19 @@
         <v>-6.050000000000068</v>
       </c>
       <c r="F10" t="n">
-        <v>-5072441.000000057</v>
+        <v>-33275.00000000038</v>
       </c>
       <c r="G10" t="n">
-        <v>2012207.999999981</v>
+        <v>1251855</v>
       </c>
       <c r="H10" t="n">
-        <v>-2084649.000000041</v>
+        <v>-449730</v>
       </c>
       <c r="I10" t="n">
-        <v>754577.9999999814</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>313.6429184545165</v>
+        <v>-111.7560035367759</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -802,22 +802,22 @@
         <v>-6.549999999999955</v>
       </c>
       <c r="F11" t="n">
-        <v>-5491650.999999962</v>
+        <v>-36024.99999999975</v>
       </c>
       <c r="G11" t="n">
-        <v>1257630</v>
+        <v>1215830</v>
       </c>
       <c r="H11" t="n">
-        <v>-6821722.000000021</v>
+        <v>-449730</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-426.5200531873739</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K11" t="n">
-        <v>4737072.99999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -837,22 +837,22 @@
         <v>-11.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-9432225</v>
+        <v>-61875</v>
       </c>
       <c r="G12" t="n">
-        <v>1257630</v>
+        <v>1153955</v>
       </c>
       <c r="H12" t="n">
-        <v>-16253947.00000002</v>
+        <v>-449730</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-1756.036537965506</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K12" t="n">
-        <v>9432225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -872,19 +872,19 @@
         <v>3.299999999999955</v>
       </c>
       <c r="F13" t="n">
-        <v>2766785.999999962</v>
+        <v>18149.99999999975</v>
       </c>
       <c r="G13" t="n">
-        <v>4024415.999999962</v>
+        <v>1172105</v>
       </c>
       <c r="H13" t="n">
-        <v>-16253947.00000002</v>
+        <v>-449730</v>
       </c>
       <c r="I13" t="n">
-        <v>2766785.999999962</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-4184.064495468268</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -907,22 +907,22 @@
         <v>-6.299999999999955</v>
       </c>
       <c r="F14" t="n">
-        <v>-5282045.999999962</v>
+        <v>-34649.99999999975</v>
       </c>
       <c r="G14" t="n">
-        <v>1257630</v>
+        <v>1137455</v>
       </c>
       <c r="H14" t="n">
-        <v>-18769207.00000002</v>
+        <v>-449730</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-3780.339238209065</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K14" t="n">
-        <v>2515260</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -942,22 +942,22 @@
         <v>-8.550000000000068</v>
       </c>
       <c r="F15" t="n">
-        <v>-7168491.000000057</v>
+        <v>-47025.00000000038</v>
       </c>
       <c r="G15" t="n">
-        <v>1257630</v>
+        <v>1090429.999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-25937698.00000008</v>
+        <v>-449730</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-4831.538617469004</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K15" t="n">
-        <v>7168491.000000057</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -977,19 +977,19 @@
         <v>1.200000000000045</v>
       </c>
       <c r="F16" t="n">
-        <v>1006104.000000038</v>
+        <v>6600.00000000025</v>
       </c>
       <c r="G16" t="n">
-        <v>2263734.000000038</v>
+        <v>1097030</v>
       </c>
       <c r="H16" t="n">
-        <v>-25937698.00000008</v>
+        <v>-449730</v>
       </c>
       <c r="I16" t="n">
-        <v>1006104.000000038</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-6676.839865171116</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1012,22 +1012,22 @@
         <v>-14.29999999999995</v>
       </c>
       <c r="F17" t="n">
-        <v>-11989405.99999996</v>
+        <v>-78649.99999999975</v>
       </c>
       <c r="G17" t="n">
-        <v>1257630</v>
+        <v>1018380</v>
       </c>
       <c r="H17" t="n">
-        <v>-36921000</v>
+        <v>-449730</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-6530.030680713216</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K17" t="n">
-        <v>10983301.99999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1047,19 +1047,19 @@
         <v>10.19999999999993</v>
       </c>
       <c r="F18" t="n">
-        <v>8551883.999999942</v>
+        <v>56099.99999999962</v>
       </c>
       <c r="G18" t="n">
-        <v>9809513.999999942</v>
+        <v>1074479.999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-36921000</v>
+        <v>-449730</v>
       </c>
       <c r="I18" t="n">
-        <v>8551883.999999942</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-9504.143531240978</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1082,19 +1082,19 @@
         <v>6.5</v>
       </c>
       <c r="F19" t="n">
-        <v>5449730</v>
+        <v>35750</v>
       </c>
       <c r="G19" t="n">
-        <v>15259243.99999994</v>
+        <v>1110229.999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-36921000</v>
+        <v>-449730</v>
       </c>
       <c r="I19" t="n">
-        <v>14001613.99999994</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-8256.265463348887</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1117,19 +1117,19 @@
         <v>-1.949999999999932</v>
       </c>
       <c r="F20" t="n">
-        <v>-1634918.999999943</v>
+        <v>-10724.99999999963</v>
       </c>
       <c r="G20" t="n">
-        <v>13624325</v>
+        <v>1099505</v>
       </c>
       <c r="H20" t="n">
-        <v>-36921000</v>
+        <v>-449730</v>
       </c>
       <c r="I20" t="n">
-        <v>12366695</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-7461.049047535294</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1152,19 +1152,19 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>3353680</v>
+        <v>22000</v>
       </c>
       <c r="G21" t="n">
-        <v>16978005</v>
+        <v>1121505</v>
       </c>
       <c r="H21" t="n">
-        <v>-36921000</v>
+        <v>-449730</v>
       </c>
       <c r="I21" t="n">
-        <v>15720375</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-7699.613972279364</v>
+        <v>-115.7687622303027</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>

--- a/logs/logs_mar.xlsx
+++ b/logs/logs_mar.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,15 +458,10 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Interest_Profit</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>Interest_Flow</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Margin_call</t>
         </is>
@@ -490,18 +485,15 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1257630</v>
+        <v>4275942</v>
       </c>
       <c r="H2" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -522,21 +514,18 @@
         <v>2.599999999999909</v>
       </c>
       <c r="F3" t="n">
-        <v>14299.9999999995</v>
+        <v>48619.9999999983</v>
       </c>
       <c r="G3" t="n">
-        <v>1271930</v>
+        <v>4324561.999999998</v>
       </c>
       <c r="H3" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>14299.99999999953</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -557,21 +546,18 @@
         <v>7.600000000000023</v>
       </c>
       <c r="F4" t="n">
-        <v>41800.00000000012</v>
+        <v>142120.0000000004</v>
       </c>
       <c r="G4" t="n">
-        <v>1313730</v>
+        <v>4466681.999999998</v>
       </c>
       <c r="H4" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>56099.99999999977</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-113.6821277096688</v>
-      </c>
-      <c r="K4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -592,21 +578,18 @@
         <v>15.25</v>
       </c>
       <c r="F5" t="n">
-        <v>83875</v>
+        <v>285175</v>
       </c>
       <c r="G5" t="n">
-        <v>1397605</v>
+        <v>4751856.999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>139974.9999999998</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-107.582734495508</v>
-      </c>
-      <c r="K5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -627,21 +610,18 @@
         <v>-3.299999999999955</v>
       </c>
       <c r="F6" t="n">
-        <v>-18149.99999999975</v>
+        <v>-61709.99999999915</v>
       </c>
       <c r="G6" t="n">
-        <v>1379455</v>
+        <v>4690146.999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>121825</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-95.3438204802513</v>
-      </c>
-      <c r="K6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -662,21 +642,18 @@
         <v>-13.85000000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>-76175.00000000013</v>
+        <v>-258995.0000000004</v>
       </c>
       <c r="G7" t="n">
-        <v>1303280</v>
+        <v>4431151.999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>45649.99999999977</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-97.99224121797894</v>
-      </c>
-      <c r="K7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -697,21 +674,18 @@
         <v>-10.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-56375</v>
+        <v>-191675</v>
       </c>
       <c r="G8" t="n">
-        <v>1246905</v>
+        <v>4239476.999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-109.1075827990482</v>
-      </c>
-      <c r="K8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -732,21 +706,18 @@
         <v>6.950000000000045</v>
       </c>
       <c r="F9" t="n">
-        <v>38225.00000000025</v>
+        <v>129965.0000000008</v>
       </c>
       <c r="G9" t="n">
-        <v>1285130</v>
+        <v>4369442</v>
       </c>
       <c r="H9" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>27500</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -767,21 +738,18 @@
         <v>-6.050000000000068</v>
       </c>
       <c r="F10" t="n">
-        <v>-33275.00000000038</v>
+        <v>-113135.0000000013</v>
       </c>
       <c r="G10" t="n">
-        <v>1251855</v>
+        <v>4256306.999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>-111.7560035367759</v>
-      </c>
-      <c r="K10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -802,21 +770,18 @@
         <v>-6.549999999999955</v>
       </c>
       <c r="F11" t="n">
-        <v>-36024.99999999975</v>
+        <v>-122484.9999999992</v>
       </c>
       <c r="G11" t="n">
-        <v>1215830</v>
+        <v>4133822</v>
       </c>
       <c r="H11" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -837,21 +802,18 @@
         <v>-11.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-61875</v>
+        <v>-210375</v>
       </c>
       <c r="G12" t="n">
-        <v>1153955</v>
+        <v>3923447</v>
       </c>
       <c r="H12" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -872,21 +834,18 @@
         <v>3.299999999999955</v>
       </c>
       <c r="F13" t="n">
-        <v>18149.99999999975</v>
+        <v>61709.99999999915</v>
       </c>
       <c r="G13" t="n">
-        <v>1172105</v>
+        <v>3985156.999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -907,21 +866,18 @@
         <v>-6.299999999999955</v>
       </c>
       <c r="F14" t="n">
-        <v>-34649.99999999975</v>
+        <v>-117809.9999999992</v>
       </c>
       <c r="G14" t="n">
-        <v>1137455</v>
+        <v>3867347</v>
       </c>
       <c r="H14" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -942,21 +898,18 @@
         <v>-8.550000000000068</v>
       </c>
       <c r="F15" t="n">
-        <v>-47025.00000000038</v>
+        <v>-159885.0000000013</v>
       </c>
       <c r="G15" t="n">
-        <v>1090429.999999999</v>
+        <v>3707461.999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -977,21 +930,18 @@
         <v>1.200000000000045</v>
       </c>
       <c r="F16" t="n">
-        <v>6600.00000000025</v>
+        <v>22440.00000000085</v>
       </c>
       <c r="G16" t="n">
-        <v>1097030</v>
+        <v>3729902</v>
       </c>
       <c r="H16" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1012,21 +962,18 @@
         <v>-14.29999999999995</v>
       </c>
       <c r="F17" t="n">
-        <v>-78649.99999999975</v>
+        <v>-267409.9999999991</v>
       </c>
       <c r="G17" t="n">
-        <v>1018380</v>
+        <v>3462492</v>
       </c>
       <c r="H17" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1047,21 +994,18 @@
         <v>10.19999999999993</v>
       </c>
       <c r="F18" t="n">
-        <v>56099.99999999962</v>
+        <v>190739.9999999987</v>
       </c>
       <c r="G18" t="n">
-        <v>1074479.999999999</v>
+        <v>3653231.999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1082,21 +1026,18 @@
         <v>6.5</v>
       </c>
       <c r="F19" t="n">
-        <v>35750</v>
+        <v>121550</v>
       </c>
       <c r="G19" t="n">
-        <v>1110229.999999999</v>
+        <v>3774781.999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1117,21 +1058,18 @@
         <v>-1.949999999999932</v>
       </c>
       <c r="F20" t="n">
-        <v>-10724.99999999963</v>
+        <v>-36464.99999999873</v>
       </c>
       <c r="G20" t="n">
-        <v>1099505</v>
+        <v>3738317</v>
       </c>
       <c r="H20" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1152,21 +1090,18 @@
         <v>4</v>
       </c>
       <c r="F21" t="n">
-        <v>22000</v>
+        <v>74800</v>
       </c>
       <c r="G21" t="n">
-        <v>1121505</v>
+        <v>3813117</v>
       </c>
       <c r="H21" t="n">
-        <v>-449730</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-115.7687622303027</v>
-      </c>
-      <c r="K21" t="n">
         <v>0</v>
       </c>
     </row>
